--- a/Stueckliste_Heimnetzwerk.xlsx
+++ b/Stueckliste_Heimnetzwerk.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Stückliste" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Endnutzergeräte" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="58">
   <si>
     <t xml:space="preserve">Stückliste – Heimnetzwerk Auftrag G</t>
   </si>
   <si>
-    <t xml:space="preserve">Alle Preise in CHF inkl. MwSt.  ·  Quelle: digitec.ch  ·  Stand: Mai 2026</t>
+    <t xml:space="preserve">Alle Preise in CHF inkl. MwSt. · Quelle: digitec.ch · Stand: Mai 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Pos.</t>
@@ -55,7 +56,7 @@
   </si>
   <si>
     <t xml:space="preserve">Sunrise Connect Box 3
-(wird vom ISP gestellt)</t>
+(wird vom ISP gestellt, nicht im Handel erhältlich)</t>
   </si>
   <si>
     <t xml:space="preserve">Router</t>
@@ -85,7 +86,8 @@
     <t xml:space="preserve">https://www.digitec.ch/de/s1/product/tp-link-tl-sg108-8-ports-netzwerk-switch-737152</t>
   </si>
   <si>
-    <t xml:space="preserve">ASUS RT-BE58U</t>
+    <t xml:space="preserve">ASUS RT-BE58U
+ASUS RT-BE58U</t>
   </si>
   <si>
     <t xml:space="preserve">Router / Access Point</t>
@@ -127,7 +129,79 @@
     <t xml:space="preserve">https://www.digitec.ch/de/s1/product/inline-patchkabel-slim-sftp-cat6a-30-m-netzwerkkabel-38913357</t>
   </si>
   <si>
-    <t xml:space="preserve">Gesamtkosten (ohne Pos. 1 – ISP-gestellt)</t>
+    <t xml:space="preserve">Gesamtkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stückliste – Heimnetzwerk Auftrag G  ·  Endnutzergeräte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alle Preise in CHF inkl. MwSt.  ·  Quelle: digitec.ch  ·  Stand: Mai 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple iPhone 16 Pro, 128 GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smartphone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digitec.ch/de/s1/product/apple-iphone-16-pro-128-gb-black-titanium-630-sim-esim-5g-smartphone-49221230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple MacBook Air M3 2024, 13.6", 8 GB / 256 GB (CH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digitec.ch/de/s1/product/apple-macbook-air-2024-1360-m3-8-gb-256-gb-ch-notebook-43366901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstbau-PC (Basic)
+Komponenten selbst zusammengestellt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop-PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstbau – kein Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstbau-PC (Mid-Range)
+Komponenten selbst zusammengestellt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstbau-PC (High-End)
+Komponenten selbst zusammengestellt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Crystal UHD 4K Fernseher 50" (UE50U8072F, 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernseher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digitec.ch/de/s1/product/samsung-fernseher-ue50u8072fuxxh-uhd-fernseher-50-led-4k-2025-tv-57580115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP Color Laser MFP 178nw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digitec.ch/de/s1/product/hp-color-laser-mfp-178nw-laser-farbe-drucker-11600155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gigaset Desk 200 (schnurgebunden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Festnetztelefon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digitec.ch/de/s1/product/gigaset-desk-200-sw-schnurgebunden-telefon-24114532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamtkosten Endnutzergeräte</t>
   </si>
 </sst>
 </file>
@@ -138,7 +212,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,7 +261,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -204,6 +277,56 @@
       <u val="single"/>
       <sz val="9"/>
       <color rgb="FF2E5F8A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -261,7 +384,9 @@
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
@@ -274,9 +399,7 @@
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
@@ -286,7 +409,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -310,80 +433,157 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -629,18 +829,18 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -716,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>2</v>
       </c>
@@ -743,34 +943,33 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>77.9</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <f aca="false">D6*E6</f>
+      <c r="F6" s="14" t="n">
         <v>77.9</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>4</v>
       </c>
@@ -797,7 +996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
@@ -810,10 +1009,10 @@
       <c r="D8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="17" t="n">
         <v>19.3</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="17" t="n">
         <f aca="false">D8*E8</f>
         <v>19.3</v>
       </c>
@@ -824,7 +1023,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>6</v>
       </c>
@@ -851,7 +1050,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
@@ -864,10 +1063,10 @@
       <c r="D10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="17" t="n">
         <v>65.2</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="17" t="n">
         <f aca="false">D10*E10</f>
         <v>65.2</v>
       </c>
@@ -878,7 +1077,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>8</v>
       </c>
@@ -905,26 +1104,36 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+    </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="14" t="n">
-        <f aca="false">F5+F6+F7+F8+F9+F10+F11</f>
-        <v>275.4</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20" t="n">
+        <f aca="false">F5+F7+F8+F9+F10+F11</f>
+        <v>197.5</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A13:E13"/>
   </mergeCells>
   <hyperlinks>
@@ -945,4 +1154,326 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <f aca="false">D4*E4</f>
+        <v>4396</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <f aca="false">D5*E5</f>
+        <v>3897</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <f aca="false">D6*E6</f>
+        <v>300</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <f aca="false">D7*E7</f>
+        <v>2000</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <f aca="false">D8*E8</f>
+        <v>4000</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>332</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <f aca="false">D9*E9</f>
+        <v>332</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>179</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <f aca="false">D10*E10</f>
+        <v>179</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <f aca="false">D11*E11</f>
+        <v>24.7</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33" t="n">
+        <f aca="false">F4+F5+F6+F7+F8+F9+F10+F11</f>
+        <v>15128.7</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H4" r:id="rId1" display="https://www.digitec.ch/de/s1/product/apple-iphone-16-pro-128-gb-black-titanium-630-sim-esim-5g-smartphone-49221230"/>
+    <hyperlink ref="H5" r:id="rId2" display="https://www.digitec.ch/de/s1/product/apple-macbook-air-2024-1360-m3-8-gb-256-gb-ch-notebook-43366901"/>
+    <hyperlink ref="H9" r:id="rId3" display="https://www.digitec.ch/de/s1/product/samsung-fernseher-ue50u8072fuxxh-uhd-fernseher-50-led-4k-2025-tv-57580115"/>
+    <hyperlink ref="H10" r:id="rId4" display="https://www.digitec.ch/de/s1/product/hp-color-laser-mfp-178nw-laser-farbe-drucker-11600155"/>
+    <hyperlink ref="H11" r:id="rId5" display="https://www.digitec.ch/de/s1/product/gigaset-desk-200-sw-schnurgebunden-telefon-24114532"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>